--- a/etf_holdings/2026-09-15_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00993A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.24%2380</t>
+          <t>+0.21%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2380</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.55%4560</t>
+          <t>-2.85%4430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4560</v>
+        <v>4430</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.37%5345</t>
+          <t>-4.3%5115</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5345</v>
+        <v>5115</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%5620</t>
+          <t>-2.77%5440</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5620</v>
+        <v>5440</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.21%234</t>
+          <t>-5.34%221.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-5.34%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>234</v>
+        <v>221.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.78%3310</t>
+          <t>-5.89%3115</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>-5.89%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3310</v>
+        <v>3115</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.75%11990</t>
+          <t>-2.29%11715</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>11990</v>
+        <v>11715</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.58%6400</t>
+          <t>-5.7%6035</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.58%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6400</v>
+        <v>6035</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.06%473</t>
+          <t>-1.59%465.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.06%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>473</v>
+        <v>465.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.73%2270</t>
+          <t>+1.98%2315</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>+1.98%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2270</v>
+        <v>2315</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.72%970</t>
+          <t>-1.96%951</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.72%</t>
+          <t>-1.96%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>970</v>
+        <v>951</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.36%17885</t>
+          <t>-2.56%17520</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.36%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>17885</v>
+        <v>17520</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.15%1365</t>
+          <t>-2.84%1370</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.15%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.53%1875</t>
+          <t>-1.87%1840</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1875</v>
+        <v>1840</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:56</t>
+          <t>2026-09-15 21:13:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.92%798</t>
+          <t>-0.38%795</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.92%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,18 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.21%6600</t>
+          <t>-4.39%6310</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.21%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>6600</t>
-        </is>
+          <t>-4.39%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>6310</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1452,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1482,27 +1480,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2368金像電子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+4.27%1955</t>
+          <t>-4.71%972</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+4.27%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
+          <t>-4.71%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>972</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.08%104,000</t>
+          <t>2.08%200,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1511,11 +1507,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>104000</v>
+        <v>200000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1545,27 +1541,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2368金像電子</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.97%1020</t>
+          <t>+1.28%1980</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.97%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
+          <t>+1.28%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1980</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.08%200,000</t>
+          <t>2.08%104,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1574,11 +1568,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>200000</v>
+        <v>104000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,18 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.71%160</t>
+          <t>-0.31%159.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.71%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
+          <t>-0.31%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>159.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1641,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,18 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>+2.84%1085</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.31%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>1055</t>
-        </is>
+          <t>+2.84%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1085</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1704,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,18 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.11%489.5</t>
+          <t>-2.45%477.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.11%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>489.5</t>
-        </is>
+          <t>-2.45%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>477.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1767,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,18 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0%1620</t>
+          <t>+3.09%1670</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>1620</t>
-        </is>
+          <t>+3.09%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1670</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1830,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1865,18 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-2.43%181</t>
+          <t>+0.83%182.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-2.43%</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
+          <t>+0.83%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>182.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1893,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,18 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.88%535</t>
+          <t>-2.8%520</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.88%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
+          <t>-2.8%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>520</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1956,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,18 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-9.98%5995</t>
+          <t>+1%6055</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.98%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>5995</t>
-        </is>
+          <t>+1%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>6055</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2019,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,40 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>202610TX台指期貨</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-1.21%1220</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-1.21%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1220</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.71%19</t>
+          <t>1.69%134,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>19</v>
+        <v>134000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2112,40 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-7.14%1235</t>
+          <t>-2.81%138.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.14%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
+          <t>-2.81%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>138.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.69%134,000</t>
+          <t>1.67%1,147,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>134000</v>
+        <v>1147000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,40 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.42%142.5</t>
+          <t>-6.47%2025</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.42%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>142.5</t>
-        </is>
+          <t>-6.47%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>2025</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.67%1,147,000</t>
+          <t>1.57%71,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1147000</v>
+        <v>71000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,40 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>3081聯亞光電</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.7%2165</t>
+          <t>-2.55%2675</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.7%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2165</t>
-        </is>
+          <t>-2.55%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2675</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.57%71,000</t>
+          <t>1.46%52,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>71000</v>
+        <v>52000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:57</t>
+          <t>2026-09-15 21:13:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2301,40 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3081聯亞光電</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.71%2810</t>
+          <t>-2.86%221</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.71%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
+          <t>-2.86%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>221</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.46%52,000</t>
+          <t>1.31%564,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>52000</v>
+        <v>564000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2351,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2364,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.96%230.5</t>
+          <t>-8.76%5310</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.96%</t>
+          <t>-8.76%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>230.5</v>
+        <v>5310</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.31%564,000</t>
+          <t>1.31%22,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2391,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>564000</v>
+        <v>22000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2412,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2425,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6139亞翔工程</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.95%5820</t>
+          <t>+1.42%713</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+1.42%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5820</v>
+        <v>713</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.31%22,000</t>
+          <t>1.18%165,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>22000</v>
+        <v>165000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2473,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2486,30 +2456,30 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6139亞翔工程</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.85%703</t>
+          <t>-1.47%537</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>703</v>
+        <v>537</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.18%165,000</t>
+          <t>0.92%165,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2534,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2547,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.18%545</t>
+          <t>-1.29%114.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>545</v>
+        <v>114.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.92%165,000</t>
+          <t>0.75%637,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>165000</v>
+        <v>637000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2595,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2608,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>6147頎邦</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.52%116</t>
+          <t>+5.82%200</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>+5.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.75%637,000</t>
+          <t>0.71%368,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>637000</v>
+        <v>368000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2656,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2669,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6147頎邦</t>
+          <t>5289宜鼎國際</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-4.99%181</t>
+          <t>-1.16%1275</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-4.99%</t>
+          <t>-1.16%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>181</v>
+        <v>1275</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.71%368,000</t>
+          <t>0.70%52,872</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>368000</v>
+        <v>52872</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2717,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2730,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5289宜鼎國際</t>
+          <t>8210勤誠興業</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.39%1295</t>
+          <t>-1.35%874</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1295</v>
+        <v>874</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.70%52,872</t>
+          <t>0.68%75,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>52872</v>
+        <v>75000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2778,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2791,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8210勤誠興業</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.56%886</t>
+          <t>+0.26%192.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>886</v>
+        <v>192.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.68%75,000</t>
+          <t>0.61%312,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>75000</v>
+        <v>312000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2839,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2852,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>8358金居開發</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.52%192</t>
+          <t>-6.95%482</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>-6.95%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>192</v>
+        <v>482</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.61%312,000</t>
+          <t>0.57%108,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>312000</v>
+        <v>108000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2900,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2913,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8358金居開發</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-6.91%485</t>
+          <t>-3.56%3255</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.91%</t>
+          <t>-3.56%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>485</v>
+        <v>3255</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.57%108,000</t>
+          <t>0.55%16,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>108000</v>
+        <v>16000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2961,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2974,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>3131弘塑科技</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-5.18%3480</t>
+          <t>+0.43%2320</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.18%</t>
+          <t>+0.43%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3480</v>
+        <v>2320</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.55%16,000</t>
+          <t>0.52%22,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3022,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3035,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3131弘塑科技</t>
+          <t>3044健鼎科技</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-5.49%2325</t>
+          <t>-3.82%490.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-5.49%</t>
+          <t>-3.82%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2325</v>
+        <v>490.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.52%22,000</t>
+          <t>0.47%90,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>22000</v>
+        <v>90000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3083,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3096,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3044健鼎科技</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.39%510</t>
+          <t>-0.78%1920</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>510</v>
+        <v>1920</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.47%90,000</t>
+          <t>0.47%24,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3123,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>90000</v>
+        <v>24000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3144,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3157,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>6239力成</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-3.63%1990</t>
+          <t>-1.29%268</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.63%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1990</v>
+        <v>268</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.47%24,000</t>
+          <t>0.46%165,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>24000</v>
+        <v>165000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3205,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 00:02:58</t>
+          <t>2026-09-15 21:13:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3218,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6239力成</t>
+          <t>2347聯強</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.55%271.5</t>
+          <t>-1.23%88.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>271.5</v>
+        <v>88.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.46%165,000</t>
+          <t>0.41%448,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>165000</v>
+        <v>448000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3266,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:00</t>
+          <t>2026-09-15 21:13:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3279,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2347聯強</t>
+          <t>3702大聯大</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.67%89.6</t>
+          <t>0%107</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>89.59999999999999</v>
+        <v>107</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.41%448,000</t>
+          <t>0.39%359,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>448000</v>
+        <v>359000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3327,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:00</t>
+          <t>2026-09-15 21:13:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3340,25 +3310,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3702大聯大</t>
+          <t>6415矽力*-KY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.47%107</t>
+          <t>-1.93%406</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>107</v>
+        <v>406</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.39%359,000</t>
+          <t>0.39%93,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3367,11 +3337,11 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>359000</v>
+        <v>93000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3388,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:00</t>
+          <t>2026-09-15 21:13:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3401,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6415矽力*-KY</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+3.24%414</t>
+          <t>-1.13%218.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+3.24%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>414</v>
+        <v>218.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.39%93,000</t>
+          <t>0.37%165,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>93000</v>
+        <v>165000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3449,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:00</t>
+          <t>2026-09-15 21:13:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3462,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.23%221</t>
+          <t>-1.72%257</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.37%165,000</t>
+          <t>0.36%134,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>165000</v>
+        <v>134000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3510,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:00</t>
+          <t>2026-09-15 21:13:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3523,25 +3493,25 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3042晶技</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.57%261.5</t>
+          <t>+1.69%181</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>+1.69%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>261.5</v>
+        <v>181</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.36%134,000</t>
+          <t>0.36%196,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3550,11 +3520,11 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>134000</v>
+        <v>196000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3571,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-15 00:03:00</t>
+          <t>2026-09-15 21:13:25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3584,102 +3554,41 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>3042晶技</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+1.14%178</t>
+          <t>-3.53%68.3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-3.53%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>178</v>
+        <v>68.3</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.36%196,000</t>
+          <t>0.08%105,360</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>196000</v>
+        <v>105360</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-09-15 00:03:00</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2885元大金</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>+1.14%70.8</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>+1.14%</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>0.08%105,360</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>0.08%</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>105360</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-15_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:22</t>
+          <t>2026-09-15 22:23:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:23</t>
+          <t>2026-09-15 22:23:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:24</t>
+          <t>2026-09-15 22:23:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:25</t>
+          <t>2026-09-15 22:23:42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:25</t>
+          <t>2026-09-15 22:23:42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:25</t>
+          <t>2026-09-15 22:23:42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:25</t>
+          <t>2026-09-15 22:23:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:25</t>
+          <t>2026-09-15 22:23:42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-15 21:13:25</t>
+          <t>2026-09-15 22:23:42</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-15_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-15_00993A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:38</t>
+          <t>2026-09-15 22:30:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:39</t>
+          <t>2026-09-15 22:30:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:40</t>
+          <t>2026-09-15 22:30:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:42</t>
+          <t>2026-09-15 22:30:08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:42</t>
+          <t>2026-09-15 22:30:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:42</t>
+          <t>2026-09-15 22:30:08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:42</t>
+          <t>2026-09-15 22:30:08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:42</t>
+          <t>2026-09-15 22:30:08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-15 22:23:42</t>
+          <t>2026-09-15 22:30:08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
